--- a/Result/profitability/3232.xlsx
+++ b/Result/profitability/3232.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.035</v>
+        <v>0.06874999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>13.65</v>
+        <v>14.69875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0275</v>
+        <v>-0.003750000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>12.7275</v>
+        <v>13.8175</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1025</v>
+        <v>-0.10875</v>
       </c>
       <c r="N4" t="n">
-        <v>12.13125</v>
+        <v>12.34125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.9</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.245</v>
+        <v>-0.18625</v>
       </c>
       <c r="N5" t="n">
-        <v>10.67125</v>
+        <v>10.34375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.255</v>
+        <v>-0.27125</v>
       </c>
       <c r="N6" t="n">
-        <v>8.943750000000001</v>
+        <v>8.61875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.52</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.485</v>
+        <v>-0.4625</v>
       </c>
       <c r="N7" t="n">
-        <v>6.86</v>
+        <v>7.577500000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.455</v>
+        <v>-0.45375</v>
       </c>
       <c r="N8" t="n">
-        <v>6.027500000000001</v>
+        <v>6.2</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0.57</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.04375000000000001</v>
+        <v>-0.04375</v>
       </c>
       <c r="N12" t="n">
         <v>7.01125</v>
@@ -2026,7 +2026,7 @@
         <v>0.22</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09624999999999999</v>
+        <v>0.09625</v>
       </c>
       <c r="N13" t="n">
         <v>6.8325</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>261</v>
+      </c>
+      <c r="D75" t="n">
+        <v>214</v>
+      </c>
+      <c r="E75" t="n">
+        <v>47</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="G75" t="n">
+        <v>11</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>11</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.30375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.379999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08358570563294965</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.678571428571428</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.620000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1277425646026329</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
